--- a/artfynd/A 37370-2023 artfynd.xlsx
+++ b/artfynd/A 37370-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37370-2023 artfynd.xlsx
+++ b/artfynd/A 37370-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1398,10 +1398,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105697377</v>
+        <v>105697581</v>
       </c>
       <c r="B8" t="n">
-        <v>95511</v>
+        <v>96251</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1414,21 +1414,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221944</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1519,10 +1519,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105697581</v>
+        <v>105697486</v>
       </c>
       <c r="B9" t="n">
-        <v>96251</v>
+        <v>106964</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1531,25 +1531,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1633,127 +1633,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr">
-        <is>
-          <t>Göteborg och Bohusläns flora 1945</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>105697486</v>
-      </c>
-      <c r="B10" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>220299</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Svinrot</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>MO: TIPPAN, Boh</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>307393.2277806551</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6513025.02788155</v>
-      </c>
-      <c r="S10" t="n">
-        <v>50</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Tanum</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>1920-01-01</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>1945-12-31</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Mora Aronsson</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Via Mora Aronsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
         <is>
           <t>Göteborg och Bohusläns flora 1945</t>
         </is>

--- a/artfynd/A 37370-2023 artfynd.xlsx
+++ b/artfynd/A 37370-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1398,10 +1398,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105697581</v>
+        <v>105697377</v>
       </c>
       <c r="B8" t="n">
-        <v>96251</v>
+        <v>95511</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1414,21 +1414,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>221944</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1519,10 +1519,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105697486</v>
+        <v>105697581</v>
       </c>
       <c r="B9" t="n">
-        <v>106964</v>
+        <v>96251</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1531,25 +1531,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1633,6 +1633,127 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr">
+        <is>
+          <t>Göteborg och Bohusläns flora 1945</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>105697486</v>
+      </c>
+      <c r="B10" t="n">
+        <v>106964</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>MO: TIPPAN, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>307393.2277806551</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6513025.02788155</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>1920-01-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1945-12-31</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Göteborg och Bohusläns flora 1945</t>
         </is>

--- a/artfynd/A 37370-2023 artfynd.xlsx
+++ b/artfynd/A 37370-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105697452</v>
+        <v>105697379</v>
       </c>
       <c r="B2" t="n">
-        <v>96926</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222295</v>
+        <v>179</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Råglosta</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Bromus secalinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>307393.2277806551</v>
+        <v>307393</v>
       </c>
       <c r="R2" t="n">
-        <v>6513025.02788155</v>
+        <v>6513025</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1920-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1945-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -799,12 +784,7 @@
         <v>105697421</v>
       </c>
       <c r="B3" t="n">
-        <v>104541</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107664</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>307393.2277806551</v>
+        <v>307393</v>
       </c>
       <c r="R3" t="n">
-        <v>6513025.02788155</v>
+        <v>6513025</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -869,19 +849,9 @@
           <t>1920-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1945-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -917,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105697400</v>
+        <v>105697581</v>
       </c>
       <c r="B4" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219955</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>307393.2277806551</v>
+        <v>307393</v>
       </c>
       <c r="R4" t="n">
-        <v>6513025.02788155</v>
+        <v>6513025</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -990,19 +955,9 @@
           <t>1920-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1945-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1038,32 +993,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105697379</v>
+        <v>105697400</v>
       </c>
       <c r="B5" t="n">
-        <v>97541</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>179</v>
+        <v>219955</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Råglosta</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bromus secalinus</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1078,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>307393.2277806551</v>
+        <v>307393</v>
       </c>
       <c r="R5" t="n">
-        <v>6513025.02788155</v>
+        <v>6513025</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1111,19 +1061,9 @@
           <t>1920-01-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1945-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1162,12 +1102,7 @@
         <v>105697504</v>
       </c>
       <c r="B6" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>307393.2277806551</v>
+        <v>307393</v>
       </c>
       <c r="R6" t="n">
-        <v>6513025.02788155</v>
+        <v>6513025</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1232,19 +1167,9 @@
           <t>1920-01-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1945-12-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1280,35 +1205,34 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105697441</v>
+        <v>105697486</v>
       </c>
       <c r="B7" t="n">
-        <v>103427</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221447</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1316,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>307393.2277806551</v>
+        <v>307393</v>
       </c>
       <c r="R7" t="n">
-        <v>6513025.02788155</v>
+        <v>6513025</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1349,21 +1273,11 @@
           <t>1920-01-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1945-12-31</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
@@ -1375,7 +1289,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1398,39 +1311,30 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105697377</v>
+        <v>105697441</v>
       </c>
       <c r="B8" t="n">
-        <v>95511</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106414</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221944</v>
+        <v>221447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1438,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>307393.2277806551</v>
+        <v>307393</v>
       </c>
       <c r="R8" t="n">
-        <v>6513025.02788155</v>
+        <v>6513025</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1471,21 +1375,11 @@
           <t>1920-01-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>1945-12-31</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
@@ -1497,6 +1391,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1519,15 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105697581</v>
+        <v>105697377</v>
       </c>
       <c r="B9" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,23 +1425,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>221944</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1559,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>307393.2277806551</v>
+        <v>307393</v>
       </c>
       <c r="R9" t="n">
-        <v>6513025.02788155</v>
+        <v>6513025</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1592,19 +1478,9 @@
           <t>1920-01-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>1945-12-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1640,15 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105697486</v>
+        <v>105697413</v>
       </c>
       <c r="B10" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,16 +1527,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>222133</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1680,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>307393.2277806551</v>
+        <v>307393</v>
       </c>
       <c r="R10" t="n">
-        <v>6513025.02788155</v>
+        <v>6513025</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1713,19 +1584,9 @@
           <t>1920-01-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>1945-12-31</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1754,6 +1615,112 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr">
+        <is>
+          <t>Göteborg och Bohusläns flora 1945</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>105697452</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99754</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>MO: TIPPAN, Boh</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>307393</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6513025</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>1920-01-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1945-12-31</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Göteborg och Bohusläns flora 1945</t>
         </is>

--- a/artfynd/A 37370-2023 artfynd.xlsx
+++ b/artfynd/A 37370-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Göteborg och Bohusläns flora 1945</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105697379</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Göteborg och Bohusläns flora 1945</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105697421</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Göteborg och Bohusläns flora 1945</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105697581</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t>Göteborg och Bohusläns flora 1945</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105697400</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
           <t>Göteborg och Bohusläns flora 1945</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105697504</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
           <t>Göteborg och Bohusläns flora 1945</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105697486</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
           <t>Göteborg och Bohusläns flora 1945</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105697441</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1513,6 +1553,11 @@
           <t>Göteborg och Bohusläns flora 1945</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105697377</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1619,6 +1664,11 @@
           <t>Göteborg och Bohusläns flora 1945</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105697413</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1725,8 +1775,25 @@
           <t>Göteborg och Bohusläns flora 1945</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105697452</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>